--- a/output/topology_excel/11181.xlsx
+++ b/output/topology_excel/11181.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>10368</v>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>434862</v>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>65</v>
-      </c>
-      <c r="J3" t="n">
         <v>15</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>434862</v>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>87672</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>434862</v>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>89544</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>70</v>
-      </c>
-      <c r="J5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>434862</v>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>23200</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10368</v>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>窗</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>434862</v>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>23200</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>窗</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31</v>
-      </c>
-      <c r="J8" t="n">
         <v>16</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>434862</v>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>10368</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>81</v>
-      </c>
-      <c r="J9" t="n">
         <v>16</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>434862</v>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>153</v>
-      </c>
-      <c r="J10" t="n">
         <v>88</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>434862</v>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>87672</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>434862</v>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>171</v>
       </c>
       <c r="F12" t="n">
-        <v>89544</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>171</v>
-      </c>
-      <c r="J12" t="n">
         <v>16</v>
       </c>
     </row>
@@ -902,37 +706,21 @@
       <c r="A13" t="n">
         <v>1</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>434862</v>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>249</v>
       </c>
       <c r="F13" t="n">
-        <v>23200</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>249</v>
-      </c>
-      <c r="J13" t="n">
         <v>116</v>
       </c>
     </row>
@@ -940,37 +728,21 @@
       <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>87672</v>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>10368</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>81</v>
-      </c>
-      <c r="J14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -978,37 +750,21 @@
       <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>87672</v>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>73</v>
-      </c>
-      <c r="J15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1016,37 +772,21 @@
       <c r="A16" t="n">
         <v>2</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>87672</v>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>312</v>
       </c>
       <c r="F16" t="n">
-        <v>89544</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>312</v>
-      </c>
-      <c r="J16" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1054,37 +794,21 @@
       <c r="A17" t="n">
         <v>3</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>10368</v>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>128</v>
       </c>
       <c r="F17" t="n">
-        <v>10001</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>128</v>
-      </c>
-      <c r="J17" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1092,37 +816,21 @@
       <c r="A18" t="n">
         <v>5</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>89544</v>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>23200</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>100</v>
-      </c>
-      <c r="J18" t="n">
         <v>16</v>
       </c>
     </row>

--- a/output/topology_excel/11181.xlsx
+++ b/output/topology_excel/11181.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,18 +674,18 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>333</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,18 +696,18 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="F15" t="n">
         <v>16</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,15 +806,15 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
         <v>6</v>
@@ -828,10 +828,1000 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>137</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>249</v>
+      </c>
+      <c r="F20" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>195</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
